--- a/backend/app/data/internal_quote_import_templates/展兴模具--工模报价表.xlsx
+++ b/backend/app/data/internal_quote_import_templates/展兴模具--工模报价表.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>河源展兴模具有限公司</t>
   </si>
@@ -179,22 +179,27 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Item No.    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="細明體"/>
+        <charset val="0"/>
+      </rPr>
+      <t>模号</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="20"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
         <charset val="0"/>
       </rPr>
-      <t xml:space="preserve">Item No.    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color indexed="8"/>
-        <rFont val="細明體"/>
-        <charset val="134"/>
-      </rPr>
-      <t>序</t>
+      <t xml:space="preserve">Item Description                                                            </t>
     </r>
     <r>
       <rPr>
@@ -203,47 +208,21 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>号</t>
+      <t>项目内容</t>
     </r>
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Material  </t>
+    </r>
+    <r>
       <rPr>
         <sz val="20"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve">Item Description                                                            </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color indexed="8"/>
+        <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>项目内容</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve">Material  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color indexed="8"/>
-        <rFont val="細明體"/>
-        <charset val="134"/>
-      </rPr>
-      <t>物料</t>
+        <charset val="0"/>
+      </rPr>
+      <t>原料</t>
     </r>
   </si>
   <si>
@@ -325,43 +304,13 @@
     <t>钢材/钢料硬度</t>
   </si>
   <si>
-    <t>日产能（啤）/机台大小</t>
+    <t>产能/机型</t>
   </si>
   <si>
     <t>胶件重量（g)</t>
   </si>
   <si>
     <t>Remark备注</t>
-  </si>
-  <si>
-    <t>水桌主体</t>
-  </si>
-  <si>
-    <t>PP</t>
-  </si>
-  <si>
-    <t>90*90*80</t>
-  </si>
-  <si>
-    <t>718H</t>
-  </si>
-  <si>
-    <t>3000/150T</t>
-  </si>
-  <si>
-    <t>顶部桌面</t>
-  </si>
-  <si>
-    <t>60*60*56</t>
-  </si>
-  <si>
-    <t>腿</t>
-  </si>
-  <si>
-    <t>65*65*56</t>
-  </si>
-  <si>
-    <t>3000/60-80T</t>
   </si>
   <si>
     <r>
@@ -886,13 +835,13 @@
     </font>
     <font>
       <sz val="20"/>
-      <color indexed="8"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="0"/>
     </font>
     <font>
       <sz val="20"/>
-      <color rgb="FF000000"/>
+      <color indexed="8"/>
       <name val="Arial"/>
       <charset val="0"/>
     </font>
@@ -1170,9 +1119,79 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
+      <b/>
+      <sz val="26"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <name val="細明體"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="細明體"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color indexed="8"/>
+      <name val="細明體"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color indexed="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <name val="PMingLiU"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Narrow"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="PMingLiU"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <name val="Arial Narrow"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
     </font>
     <font>
       <b/>
@@ -1187,75 +1206,6 @@
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="26"/>
-      <color indexed="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="26"/>
-      <name val="PMingLiU"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial Narrow"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFF0000"/>
-      <name val="PMingLiU"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="26"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="26"/>
-      <name val="細明體"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color indexed="8"/>
-      <name val="細明體"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color rgb="FF000000"/>
-      <name val="細明體"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="26"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
-      <name val="Arial Narrow"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -1743,7 +1693,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="62">
+  <cellStyleXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -1912,11 +1862,6 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2045,18 +1990,18 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="23" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="24" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2106,7 +2051,7 @@
     <xf numFmtId="7" fontId="34" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="22" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="23" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2170,7 +2115,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="62">
+  <cellStyles count="59">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -2230,9 +2175,6 @@
     <cellStyle name="千位分隔 3" xfId="56"/>
     <cellStyle name="一般_TOOLPLAN FORM" xfId="57"/>
     <cellStyle name="常规_ＰＣＢ" xfId="58"/>
-    <cellStyle name="常规 2 2" xfId="59"/>
-    <cellStyle name="常规_0930危机一发系列（公仔座）" xfId="60"/>
-    <cellStyle name="常规 7" xfId="61"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <colors>
@@ -2502,120 +2444,6 @@
         <a:ln w="9525">
           <a:noFill/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>586105</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>121285</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1604010</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>1090930</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10404475" y="6547485"/>
-          <a:ext cx="1017905" cy="969645"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>441960</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>1254125</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1898015</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>1155700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10260330" y="7680325"/>
-          <a:ext cx="1456055" cy="1171575"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>103505</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2347595</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>1184910</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9921875" y="9027160"/>
-          <a:ext cx="2244090" cy="1123950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -3126,25 +2954,25 @@
       <c r="A11" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="42" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="44" t="s">
+      <c r="F11" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="43" t="s">
+      <c r="G11" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="41" t="s">
         <v>20</v>
       </c>
       <c r="I11" s="46" t="s">
@@ -3161,107 +2989,47 @@
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="100" customHeight="1" spans="1:20">
-      <c r="A12" s="48">
-        <v>1</v>
-      </c>
-      <c r="B12" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="51">
-        <v>1</v>
-      </c>
-      <c r="E12" s="51">
-        <v>1</v>
-      </c>
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
       <c r="F12" s="52"/>
-      <c r="G12" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="54">
-        <v>237000</v>
-      </c>
-      <c r="I12" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="K12" s="46">
-        <v>32</v>
-      </c>
+      <c r="G12" s="53"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
       <c r="L12" s="55"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="100" customHeight="1" spans="1:20">
-      <c r="A13" s="48">
-        <v>2</v>
-      </c>
-      <c r="B13" s="49" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="51">
-        <v>1</v>
-      </c>
-      <c r="E13" s="51">
-        <v>1</v>
-      </c>
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
       <c r="F13" s="52"/>
-      <c r="G13" s="53" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="54">
-        <v>100000</v>
-      </c>
-      <c r="I13" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="K13" s="46">
-        <v>25</v>
-      </c>
+      <c r="G13" s="53"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
       <c r="L13" s="55"/>
       <c r="M13"/>
       <c r="N13"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="100" customHeight="1" spans="1:20">
-      <c r="A14" s="48">
-        <v>3</v>
-      </c>
-      <c r="B14" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="51">
-        <v>2</v>
-      </c>
-      <c r="E14" s="51">
-        <v>0.67</v>
-      </c>
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
       <c r="F14" s="56"/>
-      <c r="G14" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="54">
-        <v>103000</v>
-      </c>
-      <c r="I14" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="K14" s="46">
-        <v>17</v>
-      </c>
+      <c r="G14" s="53"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
       <c r="L14" s="55"/>
       <c r="M14"/>
     </row>
@@ -3327,7 +3095,7 @@
     </row>
     <row r="19" s="1" customFormat="1" ht="100" customHeight="1" spans="1:15">
       <c r="A19" s="57" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B19" s="58"/>
       <c r="C19" s="58"/>
@@ -3335,11 +3103,11 @@
       <c r="E19" s="58"/>
       <c r="F19" s="59"/>
       <c r="G19" s="60" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H19" s="61">
         <f>SUM(H12:H18)</f>
-        <v>440000</v>
+        <v>0</v>
       </c>
       <c r="I19" s="62"/>
       <c r="J19" s="62"/>
@@ -3349,10 +3117,10 @@
     </row>
     <row r="20" s="1" customFormat="1" ht="100" customHeight="1" spans="1:15">
       <c r="A20" s="64" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B20" s="65" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C20" s="65"/>
       <c r="D20" s="65"/>
@@ -3369,7 +3137,7 @@
     <row r="21" s="1" customFormat="1" ht="100" customHeight="1" spans="1:15">
       <c r="A21" s="64"/>
       <c r="B21" s="68" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C21" s="69"/>
       <c r="D21" s="69"/>
@@ -3386,7 +3154,7 @@
     <row r="22" s="1" customFormat="1" ht="70" customHeight="1" spans="1:15">
       <c r="A22" s="64"/>
       <c r="B22" s="71" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C22" s="72"/>
       <c r="D22" s="72"/>
@@ -3402,7 +3170,7 @@
     <row r="23" s="1" customFormat="1" ht="33.75" spans="1:15">
       <c r="A23" s="74"/>
       <c r="B23" s="66" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C23" s="75"/>
       <c r="D23" s="75"/>
@@ -3417,7 +3185,7 @@
     </row>
     <row r="24" s="1" customFormat="1" ht="135.75" spans="1:15">
       <c r="A24" s="77" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B24" s="78"/>
       <c r="C24" s="78"/>

--- a/backend/app/data/internal_quote_import_templates/展兴模具--工模报价表.xlsx
+++ b/backend/app/data/internal_quote_import_templates/展兴模具--工模报价表.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aalyaan\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="744"/>
+    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="744"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="17" r:id="rId1"/>
@@ -13,7 +18,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'01'!$A$1:$L$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'01'!$A$1:$M$24</definedName>
     <definedName name="cycle.time">'[1]Form-003'!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -34,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>河源展兴模具有限公司</t>
   </si>
@@ -179,6 +184,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">Item No.    </t>
     </r>
     <r>
@@ -213,6 +224,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">Material  </t>
     </r>
     <r>
@@ -304,7 +321,10 @@
     <t>钢材/钢料硬度</t>
   </si>
   <si>
-    <t>产能/机型</t>
+    <t>产能</t>
+  </si>
+  <si>
+    <t>机型</t>
   </si>
   <si>
     <t>胶件重量（g)</t>
@@ -1119,34 +1139,22 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="26"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="26"/>
-      <name val="細明體"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="細明體"/>
       <charset val="0"/>
     </font>
     <font>
-      <sz val="20"/>
-      <color indexed="8"/>
-      <name val="細明體"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="26"/>
       <color indexed="10"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <name val="Arial Narrow"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1171,21 +1179,15 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
+      <sz val="26"/>
+      <name val="宋体"/>
+      <charset val="0"/>
     </font>
     <font>
       <b/>
       <sz val="26"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
-      <name val="Arial Narrow"/>
-      <charset val="134"/>
+      <name val="細明體"/>
+      <charset val="0"/>
     </font>
     <font>
       <sz val="20"/>
@@ -1206,6 +1208,24 @@
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color indexed="8"/>
+      <name val="細明體"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -1414,7 +1434,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1596,6 +1616,17 @@
     </border>
     <border>
       <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -1717,7 +1748,7 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="4" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="4" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1729,34 +1760,34 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="6" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="6" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="7" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1863,7 +1894,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2103,6 +2134,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2752,28 +2786,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:T104"/>
+  <dimension ref="A1:U104"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.5416666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="55.225" style="1" customWidth="1"/>
+    <col min="2" max="2" width="45.6833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.2666666666667" style="8" customWidth="1"/>
     <col min="4" max="5" width="20.9083333333333" style="9" customWidth="1"/>
-    <col min="6" max="6" width="37.7166666666667" style="9" customWidth="1"/>
+    <col min="6" max="6" width="24.775" style="9" customWidth="1"/>
     <col min="7" max="7" width="25.375" style="9" customWidth="1"/>
     <col min="8" max="8" width="37.95" style="9" customWidth="1"/>
     <col min="9" max="9" width="37.275" style="9" customWidth="1"/>
     <col min="10" max="10" width="13.4083333333333" style="9" customWidth="1"/>
-    <col min="11" max="11" width="8.85833333333333" style="9" customWidth="1"/>
-    <col min="12" max="12" width="33.1833333333333" style="8" customWidth="1"/>
-    <col min="13" max="13" width="40.5" style="1" customWidth="1"/>
-    <col min="14" max="15" width="7.75" style="1"/>
-    <col min="16" max="16" width="19.125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="18.25" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="7.75" style="1"/>
+    <col min="11" max="11" width="15" style="9" customWidth="1"/>
+    <col min="12" max="12" width="23.8583333333333" style="9" customWidth="1"/>
+    <col min="13" max="13" width="33.1833333333333" style="8" customWidth="1"/>
+    <col min="14" max="14" width="40.5" style="1" customWidth="1"/>
+    <col min="15" max="16" width="7.75" style="1"/>
+    <col min="17" max="17" width="19.125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="18.25" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="30" customHeight="1" spans="1:20">
+    <row r="1" s="1" customFormat="1" ht="30" customHeight="1" spans="1:21">
       <c r="C1" s="8"/>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2783,9 +2818,10 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
-      <c r="L1" s="8"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="78.75" customHeight="1" spans="1:20">
+      <c r="L1" s="9"/>
+      <c r="M1" s="8"/>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="78.75" customHeight="1" spans="1:21">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -2800,8 +2836,9 @@
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="41.25" customHeight="1" spans="1:20">
+      <c r="M2" s="11"/>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="41.25" customHeight="1" spans="1:21">
       <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
@@ -2816,8 +2853,9 @@
       <c r="J3" s="13"/>
       <c r="K3" s="13"/>
       <c r="L3" s="13"/>
-    </row>
-    <row r="4" s="3" customFormat="1" ht="48.75" customHeight="1" spans="1:20">
+      <c r="M3" s="13"/>
+    </row>
+    <row r="4" s="3" customFormat="1" ht="48.75" customHeight="1" spans="1:21">
       <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
@@ -2832,8 +2870,9 @@
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
-    </row>
-    <row r="5" s="4" customFormat="1" ht="21.95" customHeight="1" spans="1:20">
+      <c r="M4" s="15"/>
+    </row>
+    <row r="5" s="4" customFormat="1" ht="21.95" customHeight="1" spans="1:21">
       <c r="A5" s="16" t="s">
         <v>3</v>
       </c>
@@ -2848,9 +2887,10 @@
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
       <c r="L5" s="16"/>
-      <c r="M5"/>
-    </row>
-    <row r="6" s="5" customFormat="1" ht="35.1" customHeight="1" spans="1:20">
+      <c r="M5" s="16"/>
+      <c r="N5"/>
+    </row>
+    <row r="6" s="5" customFormat="1" ht="35.1" customHeight="1" spans="1:21">
       <c r="A6" s="17" t="s">
         <v>4</v>
       </c>
@@ -2864,12 +2904,13 @@
       <c r="I6" s="20"/>
       <c r="J6" s="20"/>
       <c r="K6" s="20"/>
-      <c r="L6" s="21"/>
-      <c r="O6" s="22"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="21"/>
       <c r="P6" s="22"/>
       <c r="Q6" s="22"/>
-    </row>
-    <row r="7" s="5" customFormat="1" ht="35.1" customHeight="1" spans="1:20">
+      <c r="R6" s="22"/>
+    </row>
+    <row r="7" s="5" customFormat="1" ht="35.1" customHeight="1" spans="1:21">
       <c r="A7" s="23" t="s">
         <v>5</v>
       </c>
@@ -2884,12 +2925,13 @@
       </c>
       <c r="I7" s="26"/>
       <c r="J7" s="25"/>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="25"/>
+      <c r="L7" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="27"/>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="35.1" customHeight="1" spans="1:20">
+      <c r="M7" s="27"/>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="35.1" customHeight="1" spans="1:21">
       <c r="A8" s="23" t="s">
         <v>8</v>
       </c>
@@ -2904,21 +2946,22 @@
       </c>
       <c r="I8" s="31"/>
       <c r="J8" s="25"/>
-      <c r="K8" s="25" t="s">
+      <c r="K8" s="25"/>
+      <c r="L8" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="32" t="s">
+      <c r="M8" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="N8" s="33"/>
       <c r="O8" s="33"/>
       <c r="P8" s="33"/>
       <c r="Q8" s="33"/>
       <c r="R8" s="33"/>
       <c r="S8" s="33"/>
       <c r="T8" s="33"/>
-    </row>
-    <row r="9" s="6" customFormat="1" ht="30" customHeight="1" spans="1:20">
+      <c r="U8" s="33"/>
+    </row>
+    <row r="9" s="6" customFormat="1" ht="30" customHeight="1" spans="1:21">
       <c r="A9" s="34" t="s">
         <v>12</v>
       </c>
@@ -2932,11 +2975,12 @@
       <c r="I9" s="35"/>
       <c r="J9" s="35"/>
       <c r="K9" s="35"/>
-      <c r="L9" s="36"/>
-      <c r="M9"/>
-      <c r="N9" s="37"/>
-    </row>
-    <row r="10" s="7" customFormat="1" ht="30" customHeight="1" spans="1:20">
+      <c r="L9" s="35"/>
+      <c r="M9" s="36"/>
+      <c r="N9"/>
+      <c r="O9" s="37"/>
+    </row>
+    <row r="10" s="7" customFormat="1" ht="30" customHeight="1" spans="1:21">
       <c r="A10" s="38"/>
       <c r="B10" s="39"/>
       <c r="C10" s="39"/>
@@ -2948,9 +2992,10 @@
       <c r="I10" s="39"/>
       <c r="J10" s="39"/>
       <c r="K10" s="39"/>
-      <c r="L10" s="40"/>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="120" customHeight="1" spans="1:20">
+      <c r="L10" s="39"/>
+      <c r="M10" s="40"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="120" customHeight="1" spans="1:21">
       <c r="A11" s="41" t="s">
         <v>13</v>
       </c>
@@ -2984,11 +3029,14 @@
       <c r="K11" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="L11" s="47" t="s">
+      <c r="L11" s="46" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="100" customHeight="1" spans="1:20">
+      <c r="M11" s="47" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="100" customHeight="1" spans="1:21">
       <c r="A12" s="48"/>
       <c r="B12" s="49"/>
       <c r="C12" s="50"/>
@@ -3000,9 +3048,10 @@
       <c r="I12" s="46"/>
       <c r="J12" s="46"/>
       <c r="K12" s="46"/>
-      <c r="L12" s="55"/>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="100" customHeight="1" spans="1:20">
+      <c r="L12" s="46"/>
+      <c r="M12" s="55"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="100" customHeight="1" spans="1:21">
       <c r="A13" s="48"/>
       <c r="B13" s="49"/>
       <c r="C13" s="50"/>
@@ -3014,11 +3063,12 @@
       <c r="I13" s="46"/>
       <c r="J13" s="46"/>
       <c r="K13" s="46"/>
-      <c r="L13" s="55"/>
-      <c r="M13"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="55"/>
       <c r="N13"/>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="100" customHeight="1" spans="1:20">
+      <c r="O13"/>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="100" customHeight="1" spans="1:21">
       <c r="A14" s="48"/>
       <c r="B14" s="49"/>
       <c r="C14" s="50"/>
@@ -3030,10 +3080,11 @@
       <c r="I14" s="46"/>
       <c r="J14" s="46"/>
       <c r="K14" s="46"/>
-      <c r="L14" s="55"/>
-      <c r="M14"/>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="100" customHeight="1" spans="1:20">
+      <c r="L14" s="46"/>
+      <c r="M14" s="55"/>
+      <c r="N14"/>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="100" customHeight="1" spans="1:21">
       <c r="A15" s="48"/>
       <c r="B15" s="49"/>
       <c r="C15" s="50"/>
@@ -3045,10 +3096,11 @@
       <c r="I15" s="46"/>
       <c r="J15" s="46"/>
       <c r="K15" s="46"/>
-      <c r="L15" s="55"/>
-      <c r="M15"/>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="100" customHeight="1" spans="1:20">
+      <c r="L15" s="46"/>
+      <c r="M15" s="55"/>
+      <c r="N15"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="100" customHeight="1" spans="1:21">
       <c r="A16" s="48"/>
       <c r="B16" s="49"/>
       <c r="C16" s="50"/>
@@ -3060,10 +3112,11 @@
       <c r="I16" s="46"/>
       <c r="J16" s="46"/>
       <c r="K16" s="46"/>
-      <c r="L16" s="55"/>
-      <c r="M16"/>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="100" customHeight="1" spans="1:15">
+      <c r="L16" s="46"/>
+      <c r="M16" s="55"/>
+      <c r="N16"/>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="100" customHeight="1" spans="1:16">
       <c r="A17" s="48"/>
       <c r="B17" s="49"/>
       <c r="C17" s="50"/>
@@ -3075,10 +3128,11 @@
       <c r="I17" s="46"/>
       <c r="J17" s="46"/>
       <c r="K17" s="46"/>
-      <c r="L17" s="55"/>
-      <c r="M17"/>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="100" customHeight="1" spans="1:15">
+      <c r="L17" s="46"/>
+      <c r="M17" s="55"/>
+      <c r="N17"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="100" customHeight="1" spans="1:16">
       <c r="A18" s="48"/>
       <c r="B18" s="49"/>
       <c r="C18" s="50"/>
@@ -3090,12 +3144,13 @@
       <c r="I18" s="46"/>
       <c r="J18" s="46"/>
       <c r="K18" s="46"/>
-      <c r="L18" s="55"/>
-      <c r="M18"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="100" customHeight="1" spans="1:15">
+      <c r="L18" s="46"/>
+      <c r="M18" s="55"/>
+      <c r="N18"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="100" customHeight="1" spans="1:16">
       <c r="A19" s="57" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="58"/>
       <c r="C19" s="58"/>
@@ -3103,7 +3158,7 @@
       <c r="E19" s="58"/>
       <c r="F19" s="59"/>
       <c r="G19" s="60" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H19" s="61">
         <f>SUM(H12:H18)</f>
@@ -3111,16 +3166,17 @@
       </c>
       <c r="I19" s="62"/>
       <c r="J19" s="62"/>
-      <c r="K19" s="63"/>
-      <c r="L19" s="47"/>
-      <c r="M19"/>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="100" customHeight="1" spans="1:15">
+      <c r="K19" s="62"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="47"/>
+      <c r="N19"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="100" customHeight="1" spans="1:16">
       <c r="A20" s="64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="65" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C20" s="65"/>
       <c r="D20" s="65"/>
@@ -3130,14 +3186,15 @@
       <c r="H20" s="65"/>
       <c r="I20" s="66"/>
       <c r="J20" s="66"/>
-      <c r="K20" s="63"/>
-      <c r="L20" s="67"/>
-      <c r="M20"/>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="100" customHeight="1" spans="1:15">
+      <c r="K20" s="66"/>
+      <c r="L20" s="63"/>
+      <c r="M20" s="67"/>
+      <c r="N20"/>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="100" customHeight="1" spans="1:16">
       <c r="A21" s="64"/>
       <c r="B21" s="68" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" s="69"/>
       <c r="D21" s="69"/>
@@ -3147,14 +3204,15 @@
       <c r="H21" s="70"/>
       <c r="I21" s="68"/>
       <c r="J21" s="68"/>
-      <c r="K21" s="63"/>
-      <c r="L21" s="67"/>
-      <c r="M21"/>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="70" customHeight="1" spans="1:15">
+      <c r="K21" s="68"/>
+      <c r="L21" s="63"/>
+      <c r="M21" s="67"/>
+      <c r="N21"/>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="70" customHeight="1" spans="1:16">
       <c r="A22" s="64"/>
       <c r="B22" s="71" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C22" s="72"/>
       <c r="D22" s="72"/>
@@ -3164,13 +3222,14 @@
       <c r="H22" s="73"/>
       <c r="I22" s="71"/>
       <c r="J22" s="71"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="67"/>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="33.75" spans="1:15">
+      <c r="K22" s="71"/>
+      <c r="L22" s="63"/>
+      <c r="M22" s="67"/>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="33.75" spans="1:16">
       <c r="A23" s="74"/>
       <c r="B23" s="66" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C23" s="75"/>
       <c r="D23" s="75"/>
@@ -3180,12 +3239,13 @@
       <c r="H23" s="76"/>
       <c r="I23" s="66"/>
       <c r="J23" s="66"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="67"/>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="135.75" spans="1:15">
+      <c r="K23" s="66"/>
+      <c r="L23" s="62"/>
+      <c r="M23" s="67"/>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="135.75" spans="1:16">
       <c r="A24" s="77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="78"/>
       <c r="C24" s="78"/>
@@ -3196,8 +3256,9 @@
       <c r="H24" s="78"/>
       <c r="I24" s="79"/>
       <c r="J24" s="79"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="80"/>
+      <c r="K24" s="80"/>
+      <c r="L24" s="66"/>
+      <c r="M24" s="81"/>
     </row>
     <row r="25" s="1" customFormat="1"/>
     <row r="26" s="1" customFormat="1"/>
@@ -3205,219 +3266,232 @@
     <row r="28" s="1" customFormat="1"/>
     <row r="29" s="1" customFormat="1"/>
     <row r="30" s="1" customFormat="1"/>
-    <row r="31" s="1" customFormat="1" ht="25.5" spans="1:15">
-      <c r="M31" s="5"/>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="25.5" spans="1:15">
-      <c r="M32" s="5"/>
+    <row r="31" s="1" customFormat="1" ht="25.5" spans="1:16">
+      <c r="N31" s="5"/>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="25.5" spans="1:15">
-      <c r="M33" s="5"/>
+      <c r="P32" s="5"/>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="25.5" spans="1:15">
-      <c r="M34" s="5"/>
+      <c r="P33" s="5"/>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="25.5" spans="1:15">
-      <c r="M35" s="5"/>
+      <c r="P34" s="5"/>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="25.5" spans="1:15">
+      <c r="P35" s="5"/>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="81"/>
-      <c r="D36" s="82"/>
-      <c r="E36" s="82"/>
-      <c r="F36" s="82"/>
-      <c r="G36" s="82"/>
-      <c r="H36" s="82"/>
-      <c r="I36" s="82"/>
-      <c r="J36" s="82"/>
-      <c r="M36" s="5"/>
+      <c r="C36" s="82"/>
+      <c r="D36" s="83"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="83"/>
+      <c r="J36" s="83"/>
+      <c r="K36" s="83"/>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="25.5" spans="1:15">
+      <c r="P36" s="5"/>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="81"/>
-      <c r="D37" s="82"/>
-      <c r="E37" s="82"/>
-      <c r="F37" s="82"/>
-      <c r="G37" s="82"/>
-      <c r="H37" s="82"/>
-      <c r="I37" s="82"/>
-      <c r="J37" s="82"/>
-      <c r="M37" s="5"/>
+      <c r="C37" s="82"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="83"/>
+      <c r="I37" s="83"/>
+      <c r="J37" s="83"/>
+      <c r="K37" s="83"/>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="25.5" spans="1:15">
+      <c r="P37" s="5"/>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
-      <c r="C38" s="81"/>
-      <c r="D38" s="82"/>
-      <c r="E38" s="82"/>
-      <c r="F38" s="82"/>
-      <c r="G38" s="82"/>
-      <c r="H38" s="82"/>
-      <c r="I38" s="82"/>
-      <c r="J38" s="82"/>
-      <c r="M38" s="5"/>
+      <c r="C38" s="82"/>
+      <c r="D38" s="83"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="83"/>
+      <c r="I38" s="83"/>
+      <c r="J38" s="83"/>
+      <c r="K38" s="83"/>
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="25.5" spans="1:15">
+      <c r="P38" s="5"/>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="81"/>
-      <c r="D39" s="82"/>
-      <c r="E39" s="82"/>
-      <c r="F39" s="82"/>
-      <c r="G39" s="82"/>
-      <c r="H39" s="82"/>
-      <c r="I39" s="82"/>
-      <c r="J39" s="82"/>
-      <c r="M39" s="5"/>
+      <c r="C39" s="82"/>
+      <c r="D39" s="83"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="83"/>
+      <c r="G39" s="83"/>
+      <c r="H39" s="83"/>
+      <c r="I39" s="83"/>
+      <c r="J39" s="83"/>
+      <c r="K39" s="83"/>
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="12" customHeight="1" spans="1:15">
+      <c r="P39" s="5"/>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="12" customHeight="1" spans="1:16">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
-      <c r="C40" s="81"/>
-      <c r="D40" s="82"/>
-      <c r="E40" s="82"/>
-      <c r="F40" s="82"/>
-      <c r="G40" s="82"/>
-      <c r="H40" s="82"/>
-      <c r="I40" s="82"/>
-      <c r="J40" s="82"/>
-      <c r="K40" s="82"/>
-      <c r="N40" s="5"/>
+      <c r="C40" s="82"/>
+      <c r="D40" s="83"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="83"/>
+      <c r="I40" s="83"/>
+      <c r="J40" s="83"/>
+      <c r="K40" s="83"/>
+      <c r="L40" s="83"/>
       <c r="O40" s="5"/>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="25.5" spans="1:15">
+      <c r="P40" s="5"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
-      <c r="C41" s="81"/>
-      <c r="D41" s="82"/>
-      <c r="E41" s="82"/>
-      <c r="F41" s="82"/>
-      <c r="G41" s="82"/>
-      <c r="H41" s="82"/>
-      <c r="I41" s="82"/>
-      <c r="J41" s="82"/>
-      <c r="K41" s="82"/>
-      <c r="L41" s="81"/>
-      <c r="N41" s="5"/>
+      <c r="C41" s="82"/>
+      <c r="D41" s="83"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="83"/>
+      <c r="I41" s="83"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="83"/>
+      <c r="L41" s="83"/>
+      <c r="M41" s="82"/>
       <c r="O41" s="5"/>
-    </row>
-    <row r="42" s="1" customFormat="1" ht="25.5" spans="1:15">
+      <c r="P41" s="5"/>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
-      <c r="C42" s="81"/>
-      <c r="D42" s="82"/>
-      <c r="E42" s="82"/>
-      <c r="F42" s="82"/>
-      <c r="G42" s="82"/>
-      <c r="H42" s="82"/>
-      <c r="I42" s="82"/>
-      <c r="J42" s="82"/>
-      <c r="K42" s="82"/>
-      <c r="L42" s="81"/>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="25.5" spans="1:15">
+      <c r="C42" s="82"/>
+      <c r="D42" s="83"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="83"/>
+      <c r="G42" s="83"/>
+      <c r="H42" s="83"/>
+      <c r="I42" s="83"/>
+      <c r="J42" s="83"/>
+      <c r="K42" s="83"/>
+      <c r="L42" s="83"/>
+      <c r="M42" s="82"/>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="81"/>
-      <c r="D43" s="82"/>
-      <c r="E43" s="82"/>
-      <c r="F43" s="82"/>
-      <c r="G43" s="82"/>
-      <c r="H43" s="82"/>
-      <c r="I43" s="82"/>
-      <c r="J43" s="82"/>
-      <c r="K43" s="82"/>
-      <c r="L43" s="81"/>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="25.5" spans="1:15">
+      <c r="C43" s="82"/>
+      <c r="D43" s="83"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="83"/>
+      <c r="I43" s="83"/>
+      <c r="J43" s="83"/>
+      <c r="K43" s="83"/>
+      <c r="L43" s="83"/>
+      <c r="M43" s="82"/>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
-      <c r="C44" s="81"/>
-      <c r="D44" s="82"/>
-      <c r="E44" s="82"/>
-      <c r="F44" s="82"/>
-      <c r="G44" s="82"/>
-      <c r="H44" s="82"/>
-      <c r="I44" s="82"/>
-      <c r="J44" s="82"/>
-      <c r="K44" s="82"/>
-      <c r="L44" s="81"/>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="25.5" spans="1:15">
+      <c r="C44" s="82"/>
+      <c r="D44" s="83"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="83"/>
+      <c r="H44" s="83"/>
+      <c r="I44" s="83"/>
+      <c r="J44" s="83"/>
+      <c r="K44" s="83"/>
+      <c r="L44" s="83"/>
+      <c r="M44" s="82"/>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
-      <c r="C45" s="81"/>
-      <c r="D45" s="82"/>
-      <c r="E45" s="82"/>
-      <c r="F45" s="82"/>
-      <c r="G45" s="82"/>
-      <c r="H45" s="82"/>
-      <c r="I45" s="82"/>
-      <c r="J45" s="82"/>
-      <c r="K45" s="82"/>
-      <c r="L45" s="81"/>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="25.5" spans="1:15">
+      <c r="C45" s="82"/>
+      <c r="D45" s="83"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="83"/>
+      <c r="G45" s="83"/>
+      <c r="H45" s="83"/>
+      <c r="I45" s="83"/>
+      <c r="J45" s="83"/>
+      <c r="K45" s="83"/>
+      <c r="L45" s="83"/>
+      <c r="M45" s="82"/>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="81"/>
-      <c r="D46" s="82"/>
-      <c r="E46" s="82"/>
-      <c r="F46" s="82"/>
-      <c r="G46" s="82"/>
-      <c r="H46" s="82"/>
-      <c r="I46" s="82"/>
-      <c r="J46" s="82"/>
-      <c r="K46" s="82"/>
-      <c r="L46" s="81"/>
-    </row>
-    <row r="47" s="1" customFormat="1" ht="25.5" spans="1:15">
+      <c r="C46" s="82"/>
+      <c r="D46" s="83"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="83"/>
+      <c r="G46" s="83"/>
+      <c r="H46" s="83"/>
+      <c r="I46" s="83"/>
+      <c r="J46" s="83"/>
+      <c r="K46" s="83"/>
+      <c r="L46" s="83"/>
+      <c r="M46" s="82"/>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
-      <c r="C47" s="81"/>
-      <c r="D47" s="82"/>
-      <c r="E47" s="82"/>
-      <c r="F47" s="82"/>
-      <c r="G47" s="82"/>
-      <c r="H47" s="82"/>
-      <c r="I47" s="82"/>
-      <c r="J47" s="82"/>
-      <c r="K47" s="82"/>
-      <c r="L47" s="81"/>
-    </row>
-    <row r="48" s="1" customFormat="1" ht="25.5" spans="1:15">
+      <c r="C47" s="82"/>
+      <c r="D47" s="83"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="83"/>
+      <c r="H47" s="83"/>
+      <c r="I47" s="83"/>
+      <c r="J47" s="83"/>
+      <c r="K47" s="83"/>
+      <c r="L47" s="83"/>
+      <c r="M47" s="82"/>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="25.5" spans="1:16">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
-      <c r="C48" s="81"/>
-      <c r="D48" s="82"/>
-      <c r="E48" s="82"/>
-      <c r="F48" s="82"/>
-      <c r="G48" s="82"/>
-      <c r="H48" s="82"/>
-      <c r="I48" s="82"/>
-      <c r="J48" s="82"/>
-      <c r="K48" s="82"/>
-      <c r="L48" s="81"/>
-    </row>
-    <row r="49" s="1" customFormat="1" ht="25.5" spans="2:13">
+      <c r="C48" s="82"/>
+      <c r="D48" s="83"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="83"/>
+      <c r="H48" s="83"/>
+      <c r="I48" s="83"/>
+      <c r="J48" s="83"/>
+      <c r="K48" s="83"/>
+      <c r="L48" s="83"/>
+      <c r="M48" s="82"/>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="25.5" spans="2:14">
       <c r="C49" s="8"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
@@ -3426,23 +3500,25 @@
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
       <c r="J49" s="9"/>
-      <c r="K49" s="82"/>
-      <c r="L49" s="81"/>
-    </row>
-    <row r="50" s="1" customFormat="1" ht="25.5" spans="2:13">
+      <c r="K49" s="9"/>
+      <c r="L49" s="83"/>
+      <c r="M49" s="82"/>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="25.5" spans="2:14">
       <c r="B50" s="5"/>
       <c r="C50" s="8"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
-      <c r="F50" s="82"/>
+      <c r="F50" s="83"/>
       <c r="G50" s="9"/>
-      <c r="H50" s="81"/>
-      <c r="I50" s="81"/>
-      <c r="J50" s="81"/>
+      <c r="H50" s="82"/>
+      <c r="I50" s="82"/>
+      <c r="J50" s="82"/>
       <c r="K50" s="82"/>
-      <c r="L50" s="81"/>
-    </row>
-    <row r="51" s="1" customFormat="1" ht="25.5" spans="2:13">
+      <c r="L50" s="83"/>
+      <c r="M50" s="82"/>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="25.5" spans="2:14">
       <c r="C51" s="8"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
@@ -3451,10 +3527,11 @@
       <c r="H51" s="9"/>
       <c r="I51" s="9"/>
       <c r="J51" s="9"/>
-      <c r="K51" s="82"/>
-      <c r="L51" s="81"/>
-    </row>
-    <row r="52" s="1" customFormat="1" ht="25.5" spans="2:13">
+      <c r="K51" s="9"/>
+      <c r="L51" s="83"/>
+      <c r="M51" s="82"/>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="25.5" spans="2:14">
       <c r="C52" s="8"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
@@ -3463,10 +3540,11 @@
       <c r="H52" s="9"/>
       <c r="I52" s="9"/>
       <c r="J52" s="9"/>
-      <c r="K52" s="82"/>
-      <c r="L52" s="81"/>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="25.5" spans="2:13">
+      <c r="K52" s="9"/>
+      <c r="L52" s="83"/>
+      <c r="M52" s="82"/>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="25.5" spans="2:14">
       <c r="C53" s="8"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
@@ -3476,9 +3554,10 @@
       <c r="I53" s="9"/>
       <c r="J53" s="9"/>
       <c r="K53" s="9"/>
-      <c r="L53" s="81"/>
-    </row>
-    <row r="54" s="1" customFormat="1" ht="25.5" spans="2:13">
+      <c r="L53" s="9"/>
+      <c r="M53" s="82"/>
+    </row>
+    <row r="54" s="1" customFormat="1" ht="25.5" spans="2:14">
       <c r="C54" s="8"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
@@ -3487,10 +3566,11 @@
       <c r="H54" s="9"/>
       <c r="I54" s="9"/>
       <c r="J54" s="9"/>
-      <c r="K54" s="81"/>
-      <c r="L54" s="8"/>
-    </row>
-    <row r="55" s="1" customFormat="1" ht="25.5" spans="2:13">
+      <c r="K54" s="9"/>
+      <c r="L54" s="82"/>
+      <c r="M54" s="8"/>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="25.5" spans="2:14">
       <c r="C55" s="8"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
@@ -3500,9 +3580,10 @@
       <c r="I55" s="9"/>
       <c r="J55" s="9"/>
       <c r="K55" s="9"/>
-      <c r="L55" s="81"/>
-    </row>
-    <row r="56" s="1" customFormat="1" spans="2:13">
+      <c r="L55" s="9"/>
+      <c r="M55" s="82"/>
+    </row>
+    <row r="56" s="1" customFormat="1" spans="2:14">
       <c r="C56" s="8"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
@@ -3512,9 +3593,10 @@
       <c r="I56" s="9"/>
       <c r="J56" s="9"/>
       <c r="K56" s="9"/>
-      <c r="L56" s="8"/>
-    </row>
-    <row r="57" s="1" customFormat="1" spans="2:13">
+      <c r="L56" s="9"/>
+      <c r="M56" s="8"/>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="2:14">
       <c r="C57" s="8"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
@@ -3524,9 +3606,10 @@
       <c r="I57" s="9"/>
       <c r="J57" s="9"/>
       <c r="K57" s="9"/>
-      <c r="L57" s="8"/>
-    </row>
-    <row r="58" s="1" customFormat="1" spans="2:13">
+      <c r="L57" s="9"/>
+      <c r="M57" s="8"/>
+    </row>
+    <row r="58" s="1" customFormat="1" spans="2:14">
       <c r="C58" s="8"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
@@ -3536,9 +3619,10 @@
       <c r="I58" s="9"/>
       <c r="J58" s="9"/>
       <c r="K58" s="9"/>
-      <c r="L58" s="8"/>
-    </row>
-    <row r="59" s="1" customFormat="1" spans="2:13">
+      <c r="L58" s="9"/>
+      <c r="M58" s="8"/>
+    </row>
+    <row r="59" s="1" customFormat="1" spans="2:14">
       <c r="C59" s="8"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
@@ -3548,9 +3632,10 @@
       <c r="I59" s="9"/>
       <c r="J59" s="9"/>
       <c r="K59" s="9"/>
-      <c r="L59" s="8"/>
-    </row>
-    <row r="60" s="1" customFormat="1" spans="2:13">
+      <c r="L59" s="9"/>
+      <c r="M59" s="8"/>
+    </row>
+    <row r="60" s="1" customFormat="1" spans="2:14">
       <c r="C60" s="8"/>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
@@ -3560,9 +3645,10 @@
       <c r="I60" s="9"/>
       <c r="J60" s="9"/>
       <c r="K60" s="9"/>
-      <c r="L60" s="8"/>
-    </row>
-    <row r="61" s="1" customFormat="1" spans="2:13">
+      <c r="L60" s="9"/>
+      <c r="M60" s="8"/>
+    </row>
+    <row r="61" s="1" customFormat="1" spans="2:14">
       <c r="C61" s="8"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
@@ -3572,9 +3658,10 @@
       <c r="I61" s="9"/>
       <c r="J61" s="9"/>
       <c r="K61" s="9"/>
-      <c r="L61" s="8"/>
-    </row>
-    <row r="62" s="1" customFormat="1" spans="2:13">
+      <c r="L61" s="9"/>
+      <c r="M61" s="8"/>
+    </row>
+    <row r="62" s="1" customFormat="1" spans="2:14">
       <c r="C62" s="8"/>
       <c r="D62" s="9"/>
       <c r="E62" s="9"/>
@@ -3584,9 +3671,10 @@
       <c r="I62" s="9"/>
       <c r="J62" s="9"/>
       <c r="K62" s="9"/>
-      <c r="L62" s="8"/>
-    </row>
-    <row r="63" s="1" customFormat="1" spans="2:13">
+      <c r="L62" s="9"/>
+      <c r="M62" s="8"/>
+    </row>
+    <row r="63" s="1" customFormat="1" spans="2:14">
       <c r="C63" s="8"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
@@ -3596,9 +3684,10 @@
       <c r="I63" s="9"/>
       <c r="J63" s="9"/>
       <c r="K63" s="9"/>
-      <c r="L63" s="8"/>
-    </row>
-    <row r="64" s="1" customFormat="1" ht="25.5" spans="2:13">
+      <c r="L63" s="9"/>
+      <c r="M63" s="8"/>
+    </row>
+    <row r="64" s="1" customFormat="1" ht="25.5" spans="2:14">
       <c r="C64" s="8"/>
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
@@ -3608,10 +3697,11 @@
       <c r="I64" s="9"/>
       <c r="J64" s="9"/>
       <c r="K64" s="9"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="5"/>
-    </row>
-    <row r="65" s="1" customFormat="1" spans="1:13">
+      <c r="L64" s="9"/>
+      <c r="M64" s="8"/>
+      <c r="N64" s="5"/>
+    </row>
+    <row r="65" s="1" customFormat="1" spans="1:14">
       <c r="C65" s="8"/>
       <c r="D65" s="9"/>
       <c r="E65" s="9"/>
@@ -3621,9 +3711,10 @@
       <c r="I65" s="9"/>
       <c r="J65" s="9"/>
       <c r="K65" s="9"/>
-      <c r="L65" s="8"/>
-    </row>
-    <row r="66" s="5" customFormat="1" ht="25.5" spans="1:13">
+      <c r="L65" s="9"/>
+      <c r="M65" s="8"/>
+    </row>
+    <row r="66" s="5" customFormat="1" ht="25.5" spans="1:14">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="8"/>
@@ -3635,10 +3726,11 @@
       <c r="I66" s="9"/>
       <c r="J66" s="9"/>
       <c r="K66" s="9"/>
-      <c r="L66" s="8"/>
-      <c r="M66" s="1"/>
-    </row>
-    <row r="67" s="1" customFormat="1" spans="1:13">
+      <c r="L66" s="9"/>
+      <c r="M66" s="8"/>
+      <c r="N66" s="1"/>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="1:14">
       <c r="C67" s="8"/>
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
@@ -3648,9 +3740,10 @@
       <c r="I67" s="9"/>
       <c r="J67" s="9"/>
       <c r="K67" s="9"/>
-      <c r="L67" s="8"/>
-    </row>
-    <row r="68" s="1" customFormat="1" spans="1:13">
+      <c r="L67" s="9"/>
+      <c r="M67" s="8"/>
+    </row>
+    <row r="68" s="1" customFormat="1" spans="1:14">
       <c r="C68" s="8"/>
       <c r="D68" s="9"/>
       <c r="E68" s="9"/>
@@ -3660,9 +3753,10 @@
       <c r="I68" s="9"/>
       <c r="J68" s="9"/>
       <c r="K68" s="9"/>
-      <c r="L68" s="8"/>
-    </row>
-    <row r="69" s="1" customFormat="1" spans="1:13">
+      <c r="L68" s="9"/>
+      <c r="M68" s="8"/>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="1:14">
       <c r="C69" s="8"/>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
@@ -3672,23 +3766,25 @@
       <c r="I69" s="9"/>
       <c r="J69" s="9"/>
       <c r="K69" s="9"/>
-      <c r="L69" s="8"/>
-    </row>
-    <row r="70" s="1" customFormat="1" ht="25.5" spans="1:13">
+      <c r="L69" s="9"/>
+      <c r="M69" s="8"/>
+    </row>
+    <row r="70" s="1" customFormat="1" ht="25.5" spans="1:14">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
-      <c r="C70" s="81"/>
-      <c r="D70" s="82"/>
-      <c r="E70" s="82"/>
-      <c r="F70" s="82"/>
-      <c r="G70" s="82"/>
-      <c r="H70" s="82"/>
-      <c r="I70" s="82"/>
-      <c r="J70" s="82"/>
-      <c r="K70" s="9"/>
-      <c r="L70" s="8"/>
-    </row>
-    <row r="71" s="1" customFormat="1" spans="1:13">
+      <c r="C70" s="82"/>
+      <c r="D70" s="83"/>
+      <c r="E70" s="83"/>
+      <c r="F70" s="83"/>
+      <c r="G70" s="83"/>
+      <c r="H70" s="83"/>
+      <c r="I70" s="83"/>
+      <c r="J70" s="83"/>
+      <c r="K70" s="83"/>
+      <c r="L70" s="9"/>
+      <c r="M70" s="8"/>
+    </row>
+    <row r="71" s="1" customFormat="1" spans="1:14">
       <c r="C71" s="8"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
@@ -3698,9 +3794,10 @@
       <c r="I71" s="9"/>
       <c r="J71" s="9"/>
       <c r="K71" s="9"/>
-      <c r="L71" s="8"/>
-    </row>
-    <row r="72" s="1" customFormat="1" spans="1:13">
+      <c r="L71" s="9"/>
+      <c r="M71" s="8"/>
+    </row>
+    <row r="72" s="1" customFormat="1" spans="1:14">
       <c r="C72" s="8"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
@@ -3710,9 +3807,10 @@
       <c r="I72" s="9"/>
       <c r="J72" s="9"/>
       <c r="K72" s="9"/>
-      <c r="L72" s="8"/>
-    </row>
-    <row r="73" s="1" customFormat="1" spans="1:13">
+      <c r="L72" s="9"/>
+      <c r="M72" s="8"/>
+    </row>
+    <row r="73" s="1" customFormat="1" spans="1:14">
       <c r="C73" s="8"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
@@ -3722,9 +3820,10 @@
       <c r="I73" s="9"/>
       <c r="J73" s="9"/>
       <c r="K73" s="9"/>
-      <c r="L73" s="8"/>
-    </row>
-    <row r="74" s="1" customFormat="1" ht="25.5" spans="1:13">
+      <c r="L73" s="9"/>
+      <c r="M73" s="8"/>
+    </row>
+    <row r="74" s="1" customFormat="1" ht="25.5" spans="1:14">
       <c r="C74" s="8"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
@@ -3733,10 +3832,11 @@
       <c r="H74" s="9"/>
       <c r="I74" s="9"/>
       <c r="J74" s="9"/>
-      <c r="K74" s="82"/>
-      <c r="L74" s="8"/>
-    </row>
-    <row r="75" s="1" customFormat="1" ht="25.5" spans="1:13">
+      <c r="K74" s="9"/>
+      <c r="L74" s="83"/>
+      <c r="M74" s="8"/>
+    </row>
+    <row r="75" s="1" customFormat="1" ht="25.5" spans="1:14">
       <c r="C75" s="8"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
@@ -3746,9 +3846,10 @@
       <c r="I75" s="9"/>
       <c r="J75" s="9"/>
       <c r="K75" s="9"/>
-      <c r="L75" s="81"/>
-    </row>
-    <row r="76" s="1" customFormat="1" spans="1:13">
+      <c r="L75" s="9"/>
+      <c r="M75" s="82"/>
+    </row>
+    <row r="76" s="1" customFormat="1" spans="1:14">
       <c r="C76" s="8"/>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
@@ -3758,9 +3859,10 @@
       <c r="I76" s="9"/>
       <c r="J76" s="9"/>
       <c r="K76" s="9"/>
-      <c r="L76" s="8"/>
-    </row>
-    <row r="77" s="1" customFormat="1" spans="1:13">
+      <c r="L76" s="9"/>
+      <c r="M76" s="8"/>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="1:14">
       <c r="C77" s="8"/>
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
@@ -3770,9 +3872,10 @@
       <c r="I77" s="9"/>
       <c r="J77" s="9"/>
       <c r="K77" s="9"/>
-      <c r="L77" s="8"/>
-    </row>
-    <row r="78" s="1" customFormat="1" spans="1:13">
+      <c r="L77" s="9"/>
+      <c r="M77" s="8"/>
+    </row>
+    <row r="78" s="1" customFormat="1" spans="1:14">
       <c r="C78" s="8"/>
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
@@ -3782,9 +3885,10 @@
       <c r="I78" s="9"/>
       <c r="J78" s="9"/>
       <c r="K78" s="9"/>
-      <c r="L78" s="8"/>
-    </row>
-    <row r="79" s="1" customFormat="1" spans="1:13">
+      <c r="L78" s="9"/>
+      <c r="M78" s="8"/>
+    </row>
+    <row r="79" s="1" customFormat="1" spans="1:14">
       <c r="C79" s="8"/>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
@@ -3794,9 +3898,10 @@
       <c r="I79" s="9"/>
       <c r="J79" s="9"/>
       <c r="K79" s="9"/>
-      <c r="L79" s="8"/>
-    </row>
-    <row r="80" s="1" customFormat="1" spans="1:13">
+      <c r="L79" s="9"/>
+      <c r="M79" s="8"/>
+    </row>
+    <row r="80" s="1" customFormat="1" spans="1:14">
       <c r="C80" s="8"/>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
@@ -3806,9 +3911,10 @@
       <c r="I80" s="9"/>
       <c r="J80" s="9"/>
       <c r="K80" s="9"/>
-      <c r="L80" s="8"/>
-    </row>
-    <row r="81" s="1" customFormat="1" spans="3:12">
+      <c r="L80" s="9"/>
+      <c r="M80" s="8"/>
+    </row>
+    <row r="81" s="1" customFormat="1" spans="3:13">
       <c r="C81" s="8"/>
       <c r="D81" s="9"/>
       <c r="E81" s="9"/>
@@ -3818,9 +3924,10 @@
       <c r="I81" s="9"/>
       <c r="J81" s="9"/>
       <c r="K81" s="9"/>
-      <c r="L81" s="8"/>
-    </row>
-    <row r="82" s="1" customFormat="1" spans="3:12">
+      <c r="L81" s="9"/>
+      <c r="M81" s="8"/>
+    </row>
+    <row r="82" s="1" customFormat="1" spans="3:13">
       <c r="C82" s="8"/>
       <c r="D82" s="9"/>
       <c r="E82" s="9"/>
@@ -3830,9 +3937,10 @@
       <c r="I82" s="9"/>
       <c r="J82" s="9"/>
       <c r="K82" s="9"/>
-      <c r="L82" s="8"/>
-    </row>
-    <row r="83" s="1" customFormat="1" spans="3:12">
+      <c r="L82" s="9"/>
+      <c r="M82" s="8"/>
+    </row>
+    <row r="83" s="1" customFormat="1" spans="3:13">
       <c r="C83" s="8"/>
       <c r="D83" s="9"/>
       <c r="E83" s="9"/>
@@ -3842,9 +3950,10 @@
       <c r="I83" s="9"/>
       <c r="J83" s="9"/>
       <c r="K83" s="9"/>
-      <c r="L83" s="8"/>
-    </row>
-    <row r="84" s="1" customFormat="1" spans="3:12">
+      <c r="L83" s="9"/>
+      <c r="M83" s="8"/>
+    </row>
+    <row r="84" s="1" customFormat="1" spans="3:13">
       <c r="C84" s="8"/>
       <c r="D84" s="9"/>
       <c r="E84" s="9"/>
@@ -3854,9 +3963,10 @@
       <c r="I84" s="9"/>
       <c r="J84" s="9"/>
       <c r="K84" s="9"/>
-      <c r="L84" s="8"/>
-    </row>
-    <row r="85" s="1" customFormat="1" spans="3:12">
+      <c r="L84" s="9"/>
+      <c r="M84" s="8"/>
+    </row>
+    <row r="85" s="1" customFormat="1" spans="3:13">
       <c r="C85" s="8"/>
       <c r="D85" s="9"/>
       <c r="E85" s="9"/>
@@ -3866,9 +3976,10 @@
       <c r="I85" s="9"/>
       <c r="J85" s="9"/>
       <c r="K85" s="9"/>
-      <c r="L85" s="8"/>
-    </row>
-    <row r="86" s="1" customFormat="1" spans="3:12">
+      <c r="L85" s="9"/>
+      <c r="M85" s="8"/>
+    </row>
+    <row r="86" s="1" customFormat="1" spans="3:13">
       <c r="C86" s="8"/>
       <c r="D86" s="9"/>
       <c r="E86" s="9"/>
@@ -3878,9 +3989,10 @@
       <c r="I86" s="9"/>
       <c r="J86" s="9"/>
       <c r="K86" s="9"/>
-      <c r="L86" s="8"/>
-    </row>
-    <row r="87" s="1" customFormat="1" spans="3:12">
+      <c r="L86" s="9"/>
+      <c r="M86" s="8"/>
+    </row>
+    <row r="87" s="1" customFormat="1" spans="3:13">
       <c r="C87" s="8"/>
       <c r="D87" s="9"/>
       <c r="E87" s="9"/>
@@ -3890,9 +4002,10 @@
       <c r="I87" s="9"/>
       <c r="J87" s="9"/>
       <c r="K87" s="9"/>
-      <c r="L87" s="8"/>
-    </row>
-    <row r="88" s="1" customFormat="1" spans="3:12">
+      <c r="L87" s="9"/>
+      <c r="M87" s="8"/>
+    </row>
+    <row r="88" s="1" customFormat="1" spans="3:13">
       <c r="C88" s="8"/>
       <c r="D88" s="9"/>
       <c r="E88" s="9"/>
@@ -3902,9 +4015,10 @@
       <c r="I88" s="9"/>
       <c r="J88" s="9"/>
       <c r="K88" s="9"/>
-      <c r="L88" s="8"/>
-    </row>
-    <row r="89" s="1" customFormat="1" spans="3:12">
+      <c r="L88" s="9"/>
+      <c r="M88" s="8"/>
+    </row>
+    <row r="89" s="1" customFormat="1" spans="3:13">
       <c r="C89" s="8"/>
       <c r="D89" s="9"/>
       <c r="E89" s="9"/>
@@ -3914,9 +4028,10 @@
       <c r="I89" s="9"/>
       <c r="J89" s="9"/>
       <c r="K89" s="9"/>
-      <c r="L89" s="8"/>
-    </row>
-    <row r="90" s="1" customFormat="1" spans="3:12">
+      <c r="L89" s="9"/>
+      <c r="M89" s="8"/>
+    </row>
+    <row r="90" s="1" customFormat="1" spans="3:13">
       <c r="C90" s="8"/>
       <c r="D90" s="9"/>
       <c r="E90" s="9"/>
@@ -3926,9 +4041,10 @@
       <c r="I90" s="9"/>
       <c r="J90" s="9"/>
       <c r="K90" s="9"/>
-      <c r="L90" s="8"/>
-    </row>
-    <row r="91" s="1" customFormat="1" spans="3:12">
+      <c r="L90" s="9"/>
+      <c r="M90" s="8"/>
+    </row>
+    <row r="91" s="1" customFormat="1" spans="3:13">
       <c r="C91" s="8"/>
       <c r="D91" s="9"/>
       <c r="E91" s="9"/>
@@ -3938,9 +4054,10 @@
       <c r="I91" s="9"/>
       <c r="J91" s="9"/>
       <c r="K91" s="9"/>
-      <c r="L91" s="8"/>
-    </row>
-    <row r="92" s="1" customFormat="1" spans="3:12">
+      <c r="L91" s="9"/>
+      <c r="M91" s="8"/>
+    </row>
+    <row r="92" s="1" customFormat="1" spans="3:13">
       <c r="C92" s="8"/>
       <c r="D92" s="9"/>
       <c r="E92" s="9"/>
@@ -3950,9 +4067,10 @@
       <c r="I92" s="9"/>
       <c r="J92" s="9"/>
       <c r="K92" s="9"/>
-      <c r="L92" s="8"/>
-    </row>
-    <row r="93" s="1" customFormat="1" spans="3:12">
+      <c r="L92" s="9"/>
+      <c r="M92" s="8"/>
+    </row>
+    <row r="93" s="1" customFormat="1" spans="3:13">
       <c r="C93" s="8"/>
       <c r="D93" s="9"/>
       <c r="E93" s="9"/>
@@ -3962,9 +4080,10 @@
       <c r="I93" s="9"/>
       <c r="J93" s="9"/>
       <c r="K93" s="9"/>
-      <c r="L93" s="8"/>
-    </row>
-    <row r="94" s="1" customFormat="1" spans="3:12">
+      <c r="L93" s="9"/>
+      <c r="M93" s="8"/>
+    </row>
+    <row r="94" s="1" customFormat="1" spans="3:13">
       <c r="C94" s="8"/>
       <c r="D94" s="9"/>
       <c r="E94" s="9"/>
@@ -3974,9 +4093,10 @@
       <c r="I94" s="9"/>
       <c r="J94" s="9"/>
       <c r="K94" s="9"/>
-      <c r="L94" s="8"/>
-    </row>
-    <row r="95" s="1" customFormat="1" spans="3:12">
+      <c r="L94" s="9"/>
+      <c r="M94" s="8"/>
+    </row>
+    <row r="95" s="1" customFormat="1" spans="3:13">
       <c r="C95" s="8"/>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
@@ -3986,9 +4106,10 @@
       <c r="I95" s="9"/>
       <c r="J95" s="9"/>
       <c r="K95" s="9"/>
-      <c r="L95" s="8"/>
-    </row>
-    <row r="96" s="1" customFormat="1" spans="3:12">
+      <c r="L95" s="9"/>
+      <c r="M95" s="8"/>
+    </row>
+    <row r="96" s="1" customFormat="1" spans="3:13">
       <c r="C96" s="8"/>
       <c r="D96" s="9"/>
       <c r="E96" s="9"/>
@@ -3998,9 +4119,10 @@
       <c r="I96" s="9"/>
       <c r="J96" s="9"/>
       <c r="K96" s="9"/>
-      <c r="L96" s="8"/>
-    </row>
-    <row r="97" s="1" customFormat="1" spans="3:12">
+      <c r="L96" s="9"/>
+      <c r="M96" s="8"/>
+    </row>
+    <row r="97" s="1" customFormat="1" spans="3:13">
       <c r="C97" s="8"/>
       <c r="D97" s="9"/>
       <c r="E97" s="9"/>
@@ -4010,9 +4132,10 @@
       <c r="I97" s="9"/>
       <c r="J97" s="9"/>
       <c r="K97" s="9"/>
-      <c r="L97" s="8"/>
-    </row>
-    <row r="98" s="1" customFormat="1" spans="3:12">
+      <c r="L97" s="9"/>
+      <c r="M97" s="8"/>
+    </row>
+    <row r="98" s="1" customFormat="1" spans="3:13">
       <c r="C98" s="8"/>
       <c r="D98" s="9"/>
       <c r="E98" s="9"/>
@@ -4022,9 +4145,10 @@
       <c r="I98" s="9"/>
       <c r="J98" s="9"/>
       <c r="K98" s="9"/>
-      <c r="L98" s="8"/>
-    </row>
-    <row r="99" s="1" customFormat="1" spans="3:12">
+      <c r="L98" s="9"/>
+      <c r="M98" s="8"/>
+    </row>
+    <row r="99" s="1" customFormat="1" spans="3:13">
       <c r="C99" s="8"/>
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
@@ -4034,9 +4158,10 @@
       <c r="I99" s="9"/>
       <c r="J99" s="9"/>
       <c r="K99" s="9"/>
-      <c r="L99" s="8"/>
-    </row>
-    <row r="100" s="1" customFormat="1" spans="3:12">
+      <c r="L99" s="9"/>
+      <c r="M99" s="8"/>
+    </row>
+    <row r="100" s="1" customFormat="1" spans="3:13">
       <c r="C100" s="8"/>
       <c r="D100" s="9"/>
       <c r="E100" s="9"/>
@@ -4046,9 +4171,10 @@
       <c r="I100" s="9"/>
       <c r="J100" s="9"/>
       <c r="K100" s="9"/>
-      <c r="L100" s="8"/>
-    </row>
-    <row r="101" s="1" customFormat="1" spans="3:12">
+      <c r="L100" s="9"/>
+      <c r="M100" s="8"/>
+    </row>
+    <row r="101" s="1" customFormat="1" spans="3:13">
       <c r="C101" s="8"/>
       <c r="D101" s="9"/>
       <c r="E101" s="9"/>
@@ -4058,9 +4184,10 @@
       <c r="I101" s="9"/>
       <c r="J101" s="9"/>
       <c r="K101" s="9"/>
-      <c r="L101" s="8"/>
-    </row>
-    <row r="102" s="1" customFormat="1" spans="3:12">
+      <c r="L101" s="9"/>
+      <c r="M101" s="8"/>
+    </row>
+    <row r="102" s="1" customFormat="1" spans="3:13">
       <c r="C102" s="8"/>
       <c r="D102" s="9"/>
       <c r="E102" s="9"/>
@@ -4070,9 +4197,10 @@
       <c r="I102" s="9"/>
       <c r="J102" s="9"/>
       <c r="K102" s="9"/>
-      <c r="L102" s="8"/>
-    </row>
-    <row r="103" s="1" customFormat="1" spans="3:12">
+      <c r="L102" s="9"/>
+      <c r="M102" s="8"/>
+    </row>
+    <row r="103" s="1" customFormat="1" spans="3:13">
       <c r="C103" s="8"/>
       <c r="D103" s="9"/>
       <c r="E103" s="9"/>
@@ -4082,9 +4210,10 @@
       <c r="I103" s="9"/>
       <c r="J103" s="9"/>
       <c r="K103" s="9"/>
-      <c r="L103" s="8"/>
-    </row>
-    <row r="104" s="1" customFormat="1" ht="24" customHeight="1" spans="3:12">
+      <c r="L103" s="9"/>
+      <c r="M103" s="8"/>
+    </row>
+    <row r="104" s="1" customFormat="1" ht="24" customHeight="1" spans="3:13">
       <c r="C104" s="8"/>
       <c r="D104" s="9"/>
       <c r="E104" s="9"/>
@@ -4094,26 +4223,27 @@
       <c r="I104" s="9"/>
       <c r="J104" s="9"/>
       <c r="K104" s="9"/>
-      <c r="L104" s="8"/>
+      <c r="L104" s="9"/>
+      <c r="M104" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A5:M5"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="B23:H23"/>
-    <mergeCell ref="A9:L10"/>
+    <mergeCell ref="A9:M10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="24" orientation="portrait"/>
   <headerFooter/>
   <colBreaks count="1" manualBreakCount="1">
-    <brk id="12" max="65529" man="1"/>
+    <brk id="13" max="65529" man="1"/>
   </colBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
